--- a/data/satisfaction_detail/2026/1-6月/游客.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/游客.xlsx
@@ -475,7 +475,7 @@
         <v>9.9</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.82</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>10</v>
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="6">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>10</v>
@@ -592,7 +592,7 @@
         <v>9.82</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.82</v>
+        <v>9.84</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="13">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="15">
